--- a/data/templates/FPA工作量评估-模板.xlsx
+++ b/data/templates/FPA工作量评估-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18351" windowHeight="8211" tabRatio="691"/>
+    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="691"/>
   </bookViews>
   <sheets>
     <sheet name="FPA功能点估算" sheetId="30" r:id="rId1"/>
@@ -3833,7 +3833,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="254"/>
     </font>
     <font>
@@ -3844,7 +3844,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="254"/>
     </font>
   </fonts>
